--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23084,16 +23084,16 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>2040</v>
+        <v>2437</v>
       </c>
       <c r="O134" t="n">
-        <v>2040</v>
+        <v>2437</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>7.492536111820372</v>
+        <v>8.950642404169729</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>396522</v>
+        <v>396919</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23288,16 +23288,16 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>8415</v>
+        <v>8412</v>
       </c>
       <c r="O132" t="n">
-        <v>8415</v>
+        <v>8412</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>30.90671146125904</v>
+        <v>30.89569302580047</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -24572,16 +24572,16 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>2879</v>
+        <v>3247</v>
       </c>
       <c r="O140" t="n">
-        <v>2879</v>
+        <v>3247</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>10.57402522839748</v>
+        <v>11.92561997798076</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -25046,6 +25046,154 @@
       <c r="BC142" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>6332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>6332</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>5.172030836706432</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25082,7 +25230,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -25165,7 +25313,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -25175,7 +25323,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -25227,7 +25375,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>397364</v>
+        <v>404061</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1388</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>15.40887129129672</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>989</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>17.59242269984632</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -2002,7 +1993,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2300,9 +2291,6 @@
       <c r="P11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.4971056026286944</v>
       </c>
@@ -3008,9 +2996,6 @@
       <c r="P15" t="n">
         <v>8</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>1.988422410514778</v>
       </c>
@@ -3716,9 +3701,6 @@
       <c r="P19" t="n">
         <v>19</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>4.722503224972597</v>
       </c>
@@ -4424,9 +4406,6 @@
       <c r="P23" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>2.485528013143472</v>
       </c>
@@ -5129,9 +5108,6 @@
       <c r="O27" t="n">
         <v>575</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>6.383358063757647</v>
       </c>
@@ -5425,9 +5401,6 @@
       <c r="O29" t="n">
         <v>1000</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>17.78809170864137</v>
       </c>
@@ -5821,9 +5794,6 @@
       <c r="O31" t="n">
         <v>4</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -6218,7 +6188,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6516,9 +6486,6 @@
       <c r="P35" t="n">
         <v>12</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>2.982633615772166</v>
       </c>
@@ -7224,9 +7191,6 @@
       <c r="P39" t="n">
         <v>7</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -7932,9 +7896,6 @@
       <c r="P43" t="n">
         <v>9</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -8640,9 +8601,6 @@
       <c r="P47" t="n">
         <v>4</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.9942112052573888</v>
       </c>
@@ -9345,9 +9303,6 @@
       <c r="O51" t="n">
         <v>236</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>2.619952179211834</v>
       </c>
@@ -9641,9 +9596,6 @@
       <c r="O53" t="n">
         <v>512</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>9.107502954824383</v>
       </c>
@@ -10037,9 +9989,6 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -10434,7 +10383,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -10732,9 +10681,6 @@
       <c r="P59" t="n">
         <v>5</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -11289,9 +11235,6 @@
       <c r="O62" t="n">
         <v>44</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.4884656605310199</v>
       </c>
@@ -11440,9 +11383,6 @@
       <c r="P63" t="n">
         <v>5</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -11997,9 +11937,6 @@
       <c r="O66" t="n">
         <v>59</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.6549880448029585</v>
       </c>
@@ -12148,9 +12085,6 @@
       <c r="P67" t="n">
         <v>4</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.9942112052573888</v>
       </c>
@@ -12705,9 +12639,6 @@
       <c r="O70" t="n">
         <v>36</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.3996537222526526</v>
       </c>
@@ -12856,9 +12787,6 @@
       <c r="P71" t="n">
         <v>5</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -13413,9 +13341,6 @@
       <c r="O74" t="n">
         <v>49</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.5439731219549995</v>
       </c>
@@ -13564,9 +13489,6 @@
       <c r="P75" t="n">
         <v>6</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.491316807886083</v>
       </c>
@@ -13973,9 +13895,6 @@
       <c r="O77" t="n">
         <v>7644</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>28.07497354840928</v>
       </c>
@@ -14121,9 +14040,6 @@
       <c r="O78" t="n">
         <v>97</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>1.076844751625203</v>
       </c>
@@ -14417,9 +14333,6 @@
       <c r="O80" t="n">
         <v>170</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>3.023975590469034</v>
       </c>
@@ -14813,9 +14726,6 @@
       <c r="O82" t="n">
         <v>4</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -14961,9 +14871,6 @@
       <c r="O83" t="n">
         <v>764</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>14.44922996384477</v>
       </c>
@@ -15210,7 +15117,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -15505,9 +15412,6 @@
       <c r="O86" t="n">
         <v>27</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.2997402916894895</v>
       </c>
@@ -15656,9 +15560,6 @@
       <c r="P87" t="n">
         <v>9</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -16213,9 +16114,6 @@
       <c r="O90" t="n">
         <v>25</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.2775373071198977</v>
       </c>
@@ -16364,9 +16262,6 @@
       <c r="P91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -16921,9 +16816,6 @@
       <c r="O94" t="n">
         <v>9</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -17072,9 +16964,6 @@
       <c r="P95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -17629,9 +17518,6 @@
       <c r="O98" t="n">
         <v>11</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -17780,9 +17666,6 @@
       <c r="P99" t="n">
         <v>3</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -18189,9 +18072,6 @@
       <c r="O101" t="n">
         <v>8507</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>31.24461014865486</v>
       </c>
@@ -18337,9 +18217,6 @@
       <c r="O102" t="n">
         <v>56</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.6216835679485708</v>
       </c>
@@ -18633,9 +18510,6 @@
       <c r="O104" t="n">
         <v>66</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>1.174014052770331</v>
       </c>
@@ -19029,9 +18903,6 @@
       <c r="O106" t="n">
         <v>7</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -19177,9 +19048,6 @@
       <c r="O107" t="n">
         <v>834</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>15.77311229037505</v>
       </c>
@@ -19426,7 +19294,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -19721,9 +19589,6 @@
       <c r="O110" t="n">
         <v>14</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -19872,9 +19737,6 @@
       <c r="P111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -20429,9 +20291,6 @@
       <c r="O114" t="n">
         <v>12</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.1332179074175509</v>
       </c>
@@ -20725,9 +20584,6 @@
       <c r="O116" t="n">
         <v>17</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -21021,9 +20877,6 @@
       <c r="O118" t="n">
         <v>7</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -21317,9 +21170,6 @@
       <c r="O120" t="n">
         <v>9602</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>35.26633909102902</v>
       </c>
@@ -21465,9 +21315,6 @@
       <c r="O121" t="n">
         <v>46</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.5106686451006117</v>
       </c>
@@ -21761,9 +21608,6 @@
       <c r="O123" t="n">
         <v>20</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.3557618341728275</v>
       </c>
@@ -22157,9 +22001,6 @@
       <c r="O125" t="n">
         <v>60</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.8131621681180257</v>
       </c>
@@ -22305,9 +22146,6 @@
       <c r="O126" t="n">
         <v>611</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>11.55560145014288</v>
       </c>
@@ -22554,7 +22392,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -22701,9 +22539,6 @@
       <c r="O128" t="n">
         <v>1361</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.111676242697008</v>
       </c>
@@ -22849,9 +22684,6 @@
       <c r="O129" t="n">
         <v>1589</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>1.297908559622003</v>
       </c>
@@ -22997,9 +22829,6 @@
       <c r="O130" t="n">
         <v>2147</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>1.7536876510437</v>
       </c>
@@ -23145,9 +22974,6 @@
       <c r="O131" t="n">
         <v>3140</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>2.564778399756506</v>
       </c>
@@ -23293,9 +23119,6 @@
       <c r="O132" t="n">
         <v>8412</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>30.89569302580047</v>
       </c>
@@ -23441,9 +23264,6 @@
       <c r="O133" t="n">
         <v>18</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.3201856507555447</v>
       </c>
@@ -23837,9 +23657,6 @@
       <c r="O135" t="n">
         <v>4044</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>3.303173200195959</v>
       </c>
@@ -23985,9 +23802,6 @@
       <c r="O136" t="n">
         <v>5482</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>4.477743690275531</v>
       </c>
@@ -24133,9 +23947,6 @@
       <c r="O137" t="n">
         <v>7006</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>5.722559703405758</v>
       </c>
@@ -24281,9 +24092,6 @@
       <c r="O138" t="n">
         <v>7921</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>6.469939396328434</v>
       </c>
@@ -24429,9 +24237,6 @@
       <c r="O139" t="n">
         <v>5706</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>4.660708773570263</v>
       </c>
@@ -24577,9 +24382,6 @@
       <c r="O140" t="n">
         <v>3247</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>11.92561997798076</v>
       </c>
@@ -24725,9 +24527,6 @@
       <c r="O141" t="n">
         <v>4</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.07115236683456549</v>
       </c>
@@ -25120,9 +24919,6 @@
       </c>
       <c r="O143" t="n">
         <v>6332</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>5.172030836706432</v>

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23220,12 +23220,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23259,95 +23259,81 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="O133" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="R133" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.6327850602333667</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -23374,7 +23360,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -23423,98 +23409,23 @@
       <c r="O134" t="n">
         <v>18</v>
       </c>
+      <c r="R134" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -23608,17 +23519,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23643,7 +23554,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23652,81 +23563,170 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>4044</v>
+        <v>18</v>
       </c>
       <c r="O135" t="n">
-        <v>4044</v>
-      </c>
-      <c r="R135" t="n">
-        <v>3.303173200195959</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23788,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23797,13 +23797,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>5482</v>
+        <v>4044</v>
       </c>
       <c r="O136" t="n">
-        <v>5482</v>
+        <v>4044</v>
       </c>
       <c r="R136" t="n">
-        <v>4.477743690275531</v>
+        <v>3.303173200195959</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23942,13 +23942,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>7006</v>
+        <v>5482</v>
       </c>
       <c r="O137" t="n">
-        <v>7006</v>
+        <v>5482</v>
       </c>
       <c r="R137" t="n">
-        <v>5.722559703405758</v>
+        <v>4.477743690275531</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -24087,13 +24087,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>7921</v>
+        <v>7006</v>
       </c>
       <c r="O138" t="n">
-        <v>7921</v>
+        <v>7006</v>
       </c>
       <c r="R138" t="n">
-        <v>6.469939396328434</v>
+        <v>5.722559703405758</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24232,13 +24232,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>5706</v>
+        <v>7921</v>
       </c>
       <c r="O139" t="n">
-        <v>5706</v>
+        <v>7921</v>
       </c>
       <c r="R139" t="n">
-        <v>4.660708773570263</v>
+        <v>6.469939396328434</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24338,12 +24338,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24368,22 +24368,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>3247</v>
+        <v>5706</v>
       </c>
       <c r="O140" t="n">
-        <v>3247</v>
+        <v>5706</v>
       </c>
       <c r="R140" t="n">
-        <v>11.92561997798076</v>
+        <v>4.660708773570263</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24416,42 +24416,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24483,12 +24483,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24522,95 +24522,81 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>4</v>
+        <v>3247</v>
       </c>
       <c r="O141" t="n">
-        <v>4</v>
+        <v>3247</v>
       </c>
       <c r="R141" t="n">
-        <v>0.07115236683456549</v>
+        <v>11.92561997798076</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24623,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -24686,98 +24672,23 @@
       <c r="O142" t="n">
         <v>4</v>
       </c>
+      <c r="R142" t="n">
+        <v>0.07115236683456549</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -24871,123 +24782,357 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>4</v>
+      </c>
+      <c r="O143" t="n">
+        <v>4</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>D004</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
         <is>
           <t>新型冠状病毒感染</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="K144" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N143" t="n">
+      <c r="N144" t="n">
         <v>6332</v>
       </c>
-      <c r="O143" t="n">
+      <c r="O144" t="n">
         <v>6332</v>
       </c>
-      <c r="R143" t="n">
+      <c r="R144" t="n">
         <v>5.172030836706432</v>
       </c>
-      <c r="S143" t="inlineStr">
+      <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO143" t="inlineStr">
+      <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP143" t="inlineStr">
+      <c r="AP144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR143" t="inlineStr">
+      <c r="AR144" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS143" t="inlineStr"/>
-      <c r="AT143" t="n">
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
         <v>0</v>
       </c>
-      <c r="AU143" t="inlineStr">
+      <c r="AU144" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV143" t="inlineStr">
+      <c r="AV144" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW143" t="inlineStr">
+      <c r="AW144" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
+      <c r="AX144" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY143" t="inlineStr">
+      <c r="AY144" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA143" t="inlineStr">
+      <c r="BA144" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB143" t="inlineStr">
+      <c r="BB144" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC143" t="inlineStr">
+      <c r="BC144" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25109,7 +25254,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -25119,7 +25264,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -25171,7 +25316,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>404061</v>
+        <v>404118</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>8412</v>
+        <v>8414</v>
       </c>
       <c r="O132" t="n">
-        <v>8412</v>
+        <v>8414</v>
       </c>
       <c r="R132" t="n">
-        <v>30.89569302580047</v>
+        <v>30.90303864943952</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -24522,13 +24522,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>3247</v>
+        <v>4204</v>
       </c>
       <c r="O141" t="n">
-        <v>3247</v>
+        <v>4204</v>
       </c>
       <c r="R141" t="n">
-        <v>11.92561997798076</v>
+        <v>15.4405008892612</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>404118</v>
+        <v>405077</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -21165,13 +21165,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>9602</v>
+        <v>9601</v>
       </c>
       <c r="O120" t="n">
-        <v>9602</v>
+        <v>9601</v>
       </c>
       <c r="R120" t="n">
-        <v>35.26633909102902</v>
+        <v>35.2626662792095</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -24522,13 +24522,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>4204</v>
+        <v>4728</v>
       </c>
       <c r="O141" t="n">
-        <v>4204</v>
+        <v>4728</v>
       </c>
       <c r="R141" t="n">
-        <v>15.4405008892612</v>
+        <v>17.36505428268957</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>405077</v>
+        <v>405600</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -24522,13 +24522,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>4728</v>
+        <v>5172</v>
       </c>
       <c r="O141" t="n">
-        <v>4728</v>
+        <v>5172</v>
       </c>
       <c r="R141" t="n">
-        <v>17.36505428268957</v>
+        <v>18.99578273055636</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24667,13 +24667,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O142" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R142" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24826,10 +24826,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O143" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -25133,6 +25133,151 @@
         </is>
       </c>
       <c r="BC144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>6578</v>
+      </c>
+      <c r="O145" t="n">
+        <v>6578</v>
+      </c>
+      <c r="R145" t="n">
+        <v>5.372965704967611</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25171,7 +25316,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -25254,7 +25399,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -25264,7 +25409,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -25316,7 +25461,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>405600</v>
+        <v>412625</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23365,12 +23365,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23404,95 +23404,84 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>18</v>
+        <v>521751</v>
       </c>
       <c r="O134" t="n">
-        <v>18</v>
+        <v>521751</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>0.3201856507555447</v>
+        <v>36.92729828703948</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23508,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -23568,98 +23557,23 @@
       <c r="O135" t="n">
         <v>18</v>
       </c>
+      <c r="R135" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -23753,17 +23667,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23788,7 +23702,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23797,81 +23711,170 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>4044</v>
+        <v>18</v>
       </c>
       <c r="O136" t="n">
-        <v>4044</v>
-      </c>
-      <c r="R136" t="n">
-        <v>3.303173200195959</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23933,7 +23936,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23942,13 +23945,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>5482</v>
+        <v>4044</v>
       </c>
       <c r="O137" t="n">
-        <v>5482</v>
+        <v>4044</v>
       </c>
       <c r="R137" t="n">
-        <v>4.477743690275531</v>
+        <v>3.303173200195959</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -24078,7 +24081,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -24087,13 +24090,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>7006</v>
+        <v>5482</v>
       </c>
       <c r="O138" t="n">
-        <v>7006</v>
+        <v>5482</v>
       </c>
       <c r="R138" t="n">
-        <v>5.722559703405758</v>
+        <v>4.477743690275531</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24223,7 +24226,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24232,13 +24235,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>7921</v>
+        <v>7006</v>
       </c>
       <c r="O139" t="n">
-        <v>7921</v>
+        <v>7006</v>
       </c>
       <c r="R139" t="n">
-        <v>6.469939396328434</v>
+        <v>5.722559703405758</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24368,7 +24371,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24377,13 +24380,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>5706</v>
+        <v>7921</v>
       </c>
       <c r="O140" t="n">
-        <v>5706</v>
+        <v>7921</v>
       </c>
       <c r="R140" t="n">
-        <v>4.660708773570263</v>
+        <v>6.469939396328434</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24483,12 +24486,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24513,22 +24516,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5172</v>
+        <v>5706</v>
       </c>
       <c r="O141" t="n">
-        <v>5172</v>
+        <v>5706</v>
       </c>
       <c r="R141" t="n">
-        <v>18.99578273055636</v>
+        <v>4.660708773570263</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24561,42 +24564,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24628,12 +24631,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24667,95 +24670,81 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>7</v>
+        <v>5172</v>
       </c>
       <c r="O142" t="n">
-        <v>7</v>
+        <v>5172</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1245166419604896</v>
+        <v>18.99578273055636</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24782,7 +24771,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -24831,98 +24820,23 @@
       <c r="O143" t="n">
         <v>7</v>
       </c>
+      <c r="R143" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -25016,17 +24930,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -25051,7 +24965,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -25060,81 +24974,170 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>6332</v>
+        <v>7</v>
       </c>
       <c r="O144" t="n">
-        <v>6332</v>
-      </c>
-      <c r="R144" t="n">
-        <v>5.172030836706432</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25196,7 +25199,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25205,13 +25208,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="O145" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="R145" t="n">
-        <v>5.372965704967611</v>
+        <v>5.172030836706432</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25278,6 +25281,151 @@
         </is>
       </c>
       <c r="BC145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>6578</v>
+      </c>
+      <c r="O146" t="n">
+        <v>6578</v>
+      </c>
+      <c r="R146" t="n">
+        <v>5.372965704967611</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25399,7 +25547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -25409,7 +25557,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -25461,7 +25609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>412625</v>
+        <v>934376</v>
       </c>
     </row>
     <row r="16">
@@ -25471,7 +25619,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>8414</v>
+        <v>8415</v>
       </c>
       <c r="O132" t="n">
-        <v>8414</v>
+        <v>8415</v>
       </c>
       <c r="R132" t="n">
-        <v>30.90303864943952</v>
+        <v>30.90671146125904</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>5172</v>
+        <v>6113</v>
       </c>
       <c r="O142" t="n">
-        <v>5172</v>
+        <v>6113</v>
       </c>
       <c r="R142" t="n">
-        <v>18.99578273055636</v>
+        <v>22.45189865272448</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>934376</v>
+        <v>935318</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>6113</v>
+        <v>6493</v>
       </c>
       <c r="O142" t="n">
-        <v>6113</v>
+        <v>6493</v>
       </c>
       <c r="R142" t="n">
-        <v>22.45189865272448</v>
+        <v>23.847567144142</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24815,13 +24815,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O143" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24974,10 +24974,10 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O144" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>935318</v>
+        <v>935700</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>6493</v>
+        <v>6661</v>
       </c>
       <c r="O142" t="n">
-        <v>6493</v>
+        <v>6661</v>
       </c>
       <c r="R142" t="n">
-        <v>23.847567144142</v>
+        <v>24.46459952982132</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>935700</v>
+        <v>935868</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>6661</v>
+        <v>6778</v>
       </c>
       <c r="O142" t="n">
-        <v>6661</v>
+        <v>6778</v>
       </c>
       <c r="R142" t="n">
-        <v>24.46459952982132</v>
+        <v>24.89431851270514</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>935868</v>
+        <v>935985</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>6778</v>
+        <v>7176</v>
       </c>
       <c r="O142" t="n">
-        <v>6778</v>
+        <v>7176</v>
       </c>
       <c r="R142" t="n">
-        <v>24.89431851270514</v>
+        <v>26.35609761687402</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>935985</v>
+        <v>936383</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23906,12 +23906,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23936,7 +23936,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23945,56 +23945,70 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>4044</v>
+        <v>469</v>
       </c>
       <c r="O137" t="n">
-        <v>4044</v>
+        <v>469</v>
       </c>
       <c r="R137" t="n">
-        <v>3.303173200195959</v>
+        <v>8.870011587752877</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -24004,17 +24018,17 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
@@ -24046,17 +24060,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24081,7 +24095,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -24090,56 +24104,145 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>5482</v>
+        <v>469</v>
       </c>
       <c r="O138" t="n">
-        <v>5482</v>
-      </c>
-      <c r="R138" t="n">
-        <v>4.477743690275531</v>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>469</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -24149,17 +24252,17 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
@@ -24226,7 +24329,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24235,13 +24338,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>7006</v>
+        <v>4044</v>
       </c>
       <c r="O139" t="n">
-        <v>7006</v>
+        <v>4044</v>
       </c>
       <c r="R139" t="n">
-        <v>5.722559703405758</v>
+        <v>3.303173200195959</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24371,7 +24474,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24380,13 +24483,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>7921</v>
+        <v>5482</v>
       </c>
       <c r="O140" t="n">
-        <v>7921</v>
+        <v>5482</v>
       </c>
       <c r="R140" t="n">
-        <v>6.469939396328434</v>
+        <v>4.477743690275531</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24516,7 +24619,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24525,13 +24628,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5706</v>
+        <v>7006</v>
       </c>
       <c r="O141" t="n">
-        <v>5706</v>
+        <v>7006</v>
       </c>
       <c r="R141" t="n">
-        <v>4.660708773570263</v>
+        <v>5.722559703405758</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24631,12 +24734,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24661,22 +24764,22 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>7176</v>
+        <v>7921</v>
       </c>
       <c r="O142" t="n">
-        <v>7176</v>
+        <v>7921</v>
       </c>
       <c r="R142" t="n">
-        <v>26.35609761687402</v>
+        <v>6.469939396328434</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24709,42 +24812,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24776,12 +24879,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24806,104 +24909,90 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N143" t="n">
-        <v>9</v>
+        <v>5706</v>
       </c>
       <c r="O143" t="n">
-        <v>9</v>
+        <v>5706</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1600928253777724</v>
+        <v>4.660708773570263</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24930,17 +25019,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24974,170 +25063,81 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>9</v>
+        <v>7961</v>
       </c>
       <c r="O144" t="n">
-        <v>9</v>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
+        <v>7961</v>
+      </c>
+      <c r="R144" t="n">
+        <v>29.23925489519705</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AT144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV144" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25169,12 +25169,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25208,81 +25208,95 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>6332</v>
+        <v>13</v>
       </c>
       <c r="O145" t="n">
-        <v>6332</v>
+        <v>13</v>
       </c>
       <c r="R145" t="n">
-        <v>5.172030836706432</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25309,123 +25323,647 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>13</v>
+      </c>
+      <c r="O146" t="n">
+        <v>13</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>D004</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
         <is>
           <t>新型冠状病毒感染</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="K147" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>6332</v>
+      </c>
+      <c r="O147" t="n">
+        <v>6332</v>
+      </c>
+      <c r="R147" t="n">
+        <v>5.172030836706432</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N146" t="n">
+      <c r="N148" t="n">
         <v>6578</v>
       </c>
-      <c r="O146" t="n">
+      <c r="O148" t="n">
         <v>6578</v>
       </c>
-      <c r="R146" t="n">
+      <c r="R148" t="n">
         <v>5.372965704967611</v>
       </c>
-      <c r="S146" t="inlineStr">
+      <c r="S148" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO146" t="inlineStr">
+      <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP146" t="inlineStr">
+      <c r="AP148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR146" t="inlineStr">
+      <c r="AR148" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS146" t="inlineStr"/>
-      <c r="AT146" t="n">
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
         <v>0</v>
       </c>
-      <c r="AU146" t="inlineStr">
+      <c r="AU148" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV146" t="inlineStr">
+      <c r="AV148" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW146" t="inlineStr">
+      <c r="AW148" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX146" t="inlineStr">
+      <c r="AX148" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr">
+      <c r="AY148" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ146" t="inlineStr">
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA146" t="inlineStr">
+      <c r="BA148" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB146" t="inlineStr">
+      <c r="BB148" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC146" t="inlineStr">
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>3896</v>
+      </c>
+      <c r="O149" t="n">
+        <v>3896</v>
+      </c>
+      <c r="R149" t="n">
+        <v>3.182285555876225</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25464,7 +26002,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -25547,7 +26085,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -25557,7 +26095,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -25577,7 +26115,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -25609,7 +26147,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>936383</v>
+        <v>941537</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -21165,13 +21165,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>9601</v>
+        <v>9602</v>
       </c>
       <c r="O120" t="n">
-        <v>9601</v>
+        <v>9602</v>
       </c>
       <c r="R120" t="n">
-        <v>35.2626662792095</v>
+        <v>35.26633909102902</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>8415</v>
+        <v>8417</v>
       </c>
       <c r="O132" t="n">
-        <v>8415</v>
+        <v>8417</v>
       </c>
       <c r="R132" t="n">
-        <v>30.90671146125904</v>
+        <v>30.91405708489807</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -25063,13 +25063,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>7961</v>
+        <v>8340</v>
       </c>
       <c r="O144" t="n">
-        <v>7961</v>
+        <v>8340</v>
       </c>
       <c r="R144" t="n">
-        <v>29.23925489519705</v>
+        <v>30.63125057479505</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>941537</v>
+        <v>941919</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -25208,13 +25208,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O145" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R145" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25367,10 +25367,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O146" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>941919</v>
+        <v>941922</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -23906,12 +23906,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23945,95 +23945,81 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>469</v>
+        <v>249</v>
       </c>
       <c r="O137" t="n">
-        <v>469</v>
+        <v>249</v>
       </c>
       <c r="R137" t="n">
-        <v>8.870011587752877</v>
+        <v>3.374622997689806</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24060,7 +24046,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -24109,98 +24095,23 @@
       <c r="O138" t="n">
         <v>469</v>
       </c>
+      <c r="R138" t="n">
+        <v>8.870011587752877</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_NZ_COVID19_MONTHLY</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -24294,17 +24205,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24329,7 +24240,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24338,56 +24249,145 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>4044</v>
+        <v>469</v>
       </c>
       <c r="O139" t="n">
-        <v>4044</v>
-      </c>
-      <c r="R139" t="n">
-        <v>3.303173200195959</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>469</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -24397,17 +24397,17 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
@@ -24474,7 +24474,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24483,13 +24483,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>5482</v>
+        <v>4044</v>
       </c>
       <c r="O140" t="n">
-        <v>5482</v>
+        <v>4044</v>
       </c>
       <c r="R140" t="n">
-        <v>4.477743690275531</v>
+        <v>3.303173200195959</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24628,13 +24628,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>7006</v>
+        <v>5482</v>
       </c>
       <c r="O141" t="n">
-        <v>7006</v>
+        <v>5482</v>
       </c>
       <c r="R141" t="n">
-        <v>5.722559703405758</v>
+        <v>4.477743690275531</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24773,13 +24773,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>7921</v>
+        <v>7006</v>
       </c>
       <c r="O142" t="n">
-        <v>7921</v>
+        <v>7006</v>
       </c>
       <c r="R142" t="n">
-        <v>6.469939396328434</v>
+        <v>5.722559703405758</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24918,13 +24918,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>5706</v>
+        <v>7921</v>
       </c>
       <c r="O143" t="n">
-        <v>5706</v>
+        <v>7921</v>
       </c>
       <c r="R143" t="n">
-        <v>4.660708773570263</v>
+        <v>6.469939396328434</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -25024,12 +25024,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -25054,22 +25054,22 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N144" t="n">
-        <v>8340</v>
+        <v>5706</v>
       </c>
       <c r="O144" t="n">
-        <v>8340</v>
+        <v>5706</v>
       </c>
       <c r="R144" t="n">
-        <v>30.63125057479505</v>
+        <v>4.660708773570263</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -25102,42 +25102,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25169,12 +25169,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25208,95 +25208,81 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>16</v>
+        <v>8689</v>
       </c>
       <c r="O145" t="n">
-        <v>16</v>
+        <v>8689</v>
       </c>
       <c r="R145" t="n">
-        <v>0.284609467338262</v>
+        <v>31.91306189980746</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25323,7 +25309,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -25372,98 +25358,23 @@
       <c r="O146" t="n">
         <v>16</v>
       </c>
+      <c r="R146" t="n">
+        <v>0.284609467338262</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN146" t="b">
-        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -25557,17 +25468,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25592,7 +25503,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25601,81 +25512,170 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>6332</v>
+        <v>16</v>
       </c>
       <c r="O147" t="n">
-        <v>6332</v>
-      </c>
-      <c r="R147" t="n">
-        <v>5.172030836706432</v>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25746,13 +25746,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="O148" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="R148" t="n">
-        <v>5.372965704967611</v>
+        <v>5.172030836706432</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25891,13 +25891,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="O149" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="R149" t="n">
-        <v>3.182285555876225</v>
+        <v>5.372965704967611</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25964,6 +25964,151 @@
         </is>
       </c>
       <c r="BC149" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>3896</v>
+      </c>
+      <c r="O150" t="n">
+        <v>3896</v>
+      </c>
+      <c r="R150" t="n">
+        <v>3.182285555876225</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -26085,7 +26230,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -26095,7 +26240,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -26147,7 +26292,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>941922</v>
+        <v>942520</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -25208,13 +25208,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>8689</v>
+        <v>8832</v>
       </c>
       <c r="O145" t="n">
-        <v>8689</v>
+        <v>8832</v>
       </c>
       <c r="R145" t="n">
-        <v>31.91306189980746</v>
+        <v>32.43827398999878</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>942520</v>
+        <v>942663</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -21271,12 +21271,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21310,17 +21310,14 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="O121" t="n">
-        <v>46</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.5106686451006117</v>
+        <v>240</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -21349,42 +21346,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21416,12 +21413,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21455,20 +21452,14 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>78908</v>
+        <v>4917</v>
       </c>
       <c r="O122" t="n">
-        <v>78908</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>1</v>
-      </c>
-      <c r="R122" t="n">
-        <v>5.584769848517227</v>
+        <v>4917</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -21497,42 +21488,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21564,12 +21555,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21603,95 +21594,78 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="O123" t="n">
-        <v>20</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.3557618341728275</v>
+        <v>36</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21718,17 +21692,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21762,170 +21736,78 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>20</v>
+        <v>1160</v>
       </c>
       <c r="O124" t="n">
-        <v>20</v>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
+        <v>1160</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP124" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AT124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV124" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21957,12 +21839,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21996,17 +21878,14 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>60</v>
+        <v>443</v>
       </c>
       <c r="O125" t="n">
-        <v>60</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.8131621681180257</v>
+        <v>443</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -22035,42 +21914,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22102,12 +21981,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22141,95 +22020,78 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>611</v>
+        <v>202</v>
       </c>
       <c r="O126" t="n">
-        <v>611</v>
-      </c>
-      <c r="R126" t="n">
-        <v>11.55560145014288</v>
+        <v>202</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22256,17 +22118,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22300,170 +22162,78 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>611</v>
+        <v>1649</v>
       </c>
       <c r="O127" t="n">
-        <v>611</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
+        <v>1649</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV127" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22495,12 +22265,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22525,7 +22295,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22534,17 +22304,14 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>1361</v>
+        <v>955</v>
       </c>
       <c r="O128" t="n">
-        <v>1361</v>
-      </c>
-      <c r="R128" t="n">
-        <v>1.111676242697008</v>
+        <v>955</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -22573,42 +22340,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22640,12 +22407,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22670,7 +22437,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22679,13 +22446,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1589</v>
+        <v>46</v>
       </c>
       <c r="O129" t="n">
-        <v>1589</v>
+        <v>46</v>
       </c>
       <c r="R129" t="n">
-        <v>1.297908559622003</v>
+        <v>0.5106686451006117</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22718,42 +22485,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -22785,12 +22552,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22815,7 +22582,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22824,13 +22591,16 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>2147</v>
+        <v>78908</v>
       </c>
       <c r="O130" t="n">
-        <v>2147</v>
+        <v>78908</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>1</v>
       </c>
       <c r="R130" t="n">
-        <v>1.7536876510437</v>
+        <v>5.584769848517227</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22863,17 +22633,17 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -22883,22 +22653,22 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -22930,12 +22700,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22960,7 +22730,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22969,81 +22739,95 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>3140</v>
+        <v>20</v>
       </c>
       <c r="O131" t="n">
-        <v>3140</v>
+        <v>20</v>
       </c>
       <c r="R131" t="n">
-        <v>2.564778399756506</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23070,17 +22854,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23105,90 +22889,179 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>8417</v>
+        <v>20</v>
       </c>
       <c r="O132" t="n">
-        <v>8417</v>
-      </c>
-      <c r="R132" t="n">
-        <v>30.91405708489807</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23220,12 +23093,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23250,22 +23123,22 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O133" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R133" t="n">
-        <v>0.6327850602333667</v>
+        <v>0.8131621681180257</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23298,42 +23171,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23365,12 +23238,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23395,68 +23268,79 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>521751</v>
+        <v>611</v>
       </c>
       <c r="O134" t="n">
-        <v>521751</v>
-      </c>
-      <c r="Q134" t="n">
+        <v>611</v>
+      </c>
+      <c r="R134" t="n">
+        <v>11.55560145014288</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
         <v>1</v>
       </c>
-      <c r="R134" t="n">
-        <v>36.92729828703948</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
-      <c r="AT134" t="n">
-        <v>0</v>
-      </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -23466,22 +23350,22 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23508,17 +23392,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23543,31 +23427,48 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>18</v>
+        <v>611</v>
       </c>
       <c r="O135" t="n">
-        <v>18</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0.3201856507555447</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>611</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_2801</t>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -23575,6 +23476,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23587,12 +23546,12 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_2801</t>
+          <t>SER_NZ_COVID19_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -23600,47 +23559,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23667,17 +23626,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23702,179 +23661,90 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>18</v>
+        <v>1361</v>
       </c>
       <c r="O136" t="n">
-        <v>18</v>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
+        <v>1361</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.111676242697008</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23906,12 +23776,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23936,22 +23806,22 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N137" t="n">
-        <v>249</v>
+        <v>1589</v>
       </c>
       <c r="O137" t="n">
-        <v>249</v>
+        <v>1589</v>
       </c>
       <c r="R137" t="n">
-        <v>3.374622997689806</v>
+        <v>1.297908559622003</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23984,42 +23854,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24051,12 +23921,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24081,79 +23951,65 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>469</v>
+        <v>2147</v>
       </c>
       <c r="O138" t="n">
-        <v>469</v>
+        <v>2147</v>
       </c>
       <c r="R138" t="n">
-        <v>8.870011587752877</v>
+        <v>1.7536876510437</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -24163,17 +24019,17 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
@@ -24205,17 +24061,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24240,154 +24096,65 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>469</v>
+        <v>3140</v>
       </c>
       <c r="O139" t="n">
-        <v>469</v>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
-        <v>1</v>
+        <v>3140</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2.564778399756506</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -24397,17 +24164,17 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
@@ -24444,12 +24211,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24474,7 +24241,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24483,13 +24250,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>4044</v>
+        <v>8417</v>
       </c>
       <c r="O140" t="n">
-        <v>4044</v>
+        <v>8417</v>
       </c>
       <c r="R140" t="n">
-        <v>3.303173200195959</v>
+        <v>30.91405708489807</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24522,42 +24289,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24589,12 +24356,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24619,7 +24386,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24628,17 +24395,14 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5482</v>
+        <v>175</v>
       </c>
       <c r="O141" t="n">
-        <v>5482</v>
-      </c>
-      <c r="R141" t="n">
-        <v>4.477743690275531</v>
+        <v>175</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -24667,42 +24431,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24734,12 +24498,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24764,7 +24528,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24773,17 +24537,14 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>7006</v>
+        <v>4127</v>
       </c>
       <c r="O142" t="n">
-        <v>7006</v>
-      </c>
-      <c r="R142" t="n">
-        <v>5.722559703405758</v>
+        <v>4127</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -24812,42 +24573,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24879,12 +24640,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24909,7 +24670,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24918,17 +24679,14 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>7921</v>
+        <v>27</v>
       </c>
       <c r="O143" t="n">
-        <v>7921</v>
-      </c>
-      <c r="R143" t="n">
-        <v>6.469939396328434</v>
+        <v>27</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -24957,42 +24715,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25024,12 +24782,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -25054,7 +24812,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -25063,17 +24821,14 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>5706</v>
+        <v>1033</v>
       </c>
       <c r="O144" t="n">
-        <v>5706</v>
-      </c>
-      <c r="R144" t="n">
-        <v>4.660708773570263</v>
+        <v>1033</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -25102,42 +24857,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25169,12 +24924,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25199,26 +24954,23 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N145" t="n">
-        <v>8832</v>
+        <v>340</v>
       </c>
       <c r="O145" t="n">
-        <v>8832</v>
-      </c>
-      <c r="R145" t="n">
-        <v>32.43827398999878</v>
+        <v>340</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -25252,12 +25004,12 @@
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -25272,12 +25024,12 @@
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
@@ -25314,12 +25066,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25344,104 +25096,87 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N146" t="n">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="O146" t="n">
-        <v>16</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0.284609467338262</v>
+        <v>198</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25468,17 +25203,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25503,179 +25238,87 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N147" t="n">
-        <v>16</v>
+        <v>1783</v>
       </c>
       <c r="O147" t="n">
-        <v>16</v>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
+        <v>1783</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP147" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AT147" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV147" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25707,12 +25350,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25737,26 +25380,23 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>6332</v>
+        <v>734</v>
       </c>
       <c r="O148" t="n">
-        <v>6332</v>
-      </c>
-      <c r="R148" t="n">
-        <v>5.172030836706432</v>
+        <v>734</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -25785,42 +25425,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25852,12 +25492,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25882,22 +25522,22 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>6578</v>
+        <v>57</v>
       </c>
       <c r="O149" t="n">
-        <v>6578</v>
+        <v>57</v>
       </c>
       <c r="R149" t="n">
-        <v>5.372965704967611</v>
+        <v>0.6327850602333667</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25930,42 +25570,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -25997,12 +25637,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26027,22 +25667,25 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>3896</v>
+        <v>521751</v>
       </c>
       <c r="O150" t="n">
-        <v>3896</v>
+        <v>521751</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>1</v>
       </c>
       <c r="R150" t="n">
-        <v>3.182285555876225</v>
+        <v>36.92729828703948</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26075,42 +25718,4490 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>18</v>
+      </c>
+      <c r="O151" t="n">
+        <v>18</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>18</v>
+      </c>
+      <c r="O152" t="n">
+        <v>18</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>249</v>
+      </c>
+      <c r="O153" t="n">
+        <v>249</v>
+      </c>
+      <c r="R153" t="n">
+        <v>3.374622997689806</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>469</v>
+      </c>
+      <c r="O154" t="n">
+        <v>469</v>
+      </c>
+      <c r="R154" t="n">
+        <v>8.870011587752877</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>469</v>
+      </c>
+      <c r="O155" t="n">
+        <v>469</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>4044</v>
+      </c>
+      <c r="O156" t="n">
+        <v>4044</v>
+      </c>
+      <c r="R156" t="n">
+        <v>3.303173200195959</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW150" t="inlineStr">
+      <c r="AW156" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX150" t="inlineStr">
+      <c r="AX156" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr">
+      <c r="AY156" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ150" t="inlineStr">
+      <c r="AZ156" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA150" t="inlineStr">
+      <c r="BA156" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB150" t="inlineStr">
+      <c r="BB156" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC150" t="inlineStr">
+      <c r="BC156" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>5482</v>
+      </c>
+      <c r="O157" t="n">
+        <v>5482</v>
+      </c>
+      <c r="R157" t="n">
+        <v>4.477743690275531</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>7006</v>
+      </c>
+      <c r="O158" t="n">
+        <v>7006</v>
+      </c>
+      <c r="R158" t="n">
+        <v>5.722559703405758</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>7921</v>
+      </c>
+      <c r="O159" t="n">
+        <v>7921</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6.469939396328434</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>5706</v>
+      </c>
+      <c r="O160" t="n">
+        <v>5706</v>
+      </c>
+      <c r="R160" t="n">
+        <v>4.660708773570263</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>9697</v>
+      </c>
+      <c r="O161" t="n">
+        <v>9697</v>
+      </c>
+      <c r="R161" t="n">
+        <v>35.61525621388341</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>216</v>
+      </c>
+      <c r="O162" t="n">
+        <v>216</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>3900</v>
+      </c>
+      <c r="O163" t="n">
+        <v>3900</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>25</v>
+      </c>
+      <c r="O164" t="n">
+        <v>25</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1205</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1205</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>319</v>
+      </c>
+      <c r="O166" t="n">
+        <v>319</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>184</v>
+      </c>
+      <c r="O167" t="n">
+        <v>184</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>2361</v>
+      </c>
+      <c r="O168" t="n">
+        <v>2361</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>715</v>
+      </c>
+      <c r="O169" t="n">
+        <v>715</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>18</v>
+      </c>
+      <c r="O170" t="n">
+        <v>18</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>18</v>
+      </c>
+      <c r="O171" t="n">
+        <v>18</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>6332</v>
+      </c>
+      <c r="O172" t="n">
+        <v>6332</v>
+      </c>
+      <c r="R172" t="n">
+        <v>5.172030836706432</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>6578</v>
+      </c>
+      <c r="O173" t="n">
+        <v>6578</v>
+      </c>
+      <c r="R173" t="n">
+        <v>5.372965704967611</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>3896</v>
+      </c>
+      <c r="O174" t="n">
+        <v>3896</v>
+      </c>
+      <c r="R174" t="n">
+        <v>3.182285555876225</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>4353</v>
+      </c>
+      <c r="O175" t="n">
+        <v>4353</v>
+      </c>
+      <c r="R175" t="n">
+        <v>3.55556699813378</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>319</v>
+      </c>
+      <c r="O176" t="n">
+        <v>319</v>
+      </c>
+      <c r="R176" t="n">
+        <v>1.171626970426813</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>3</v>
+      </c>
+      <c r="O177" t="n">
+        <v>3</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>3</v>
+      </c>
+      <c r="O178" t="n">
+        <v>3</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN178" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26147,7 +30238,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -26230,7 +30321,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
@@ -26240,7 +30331,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -26260,7 +30351,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -26292,7 +30383,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>942663</v>
+        <v>975149</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -27480,13 +27480,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9697</v>
+        <v>9714</v>
       </c>
       <c r="O161" t="n">
-        <v>9697</v>
+        <v>9714</v>
       </c>
       <c r="R161" t="n">
-        <v>35.61525621388341</v>
+        <v>35.67769401481524</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -29734,13 +29734,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>319</v>
+        <v>639</v>
       </c>
       <c r="O176" t="n">
-        <v>319</v>
+        <v>639</v>
       </c>
       <c r="R176" t="n">
-        <v>1.171626970426813</v>
+        <v>2.346926752673146</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>975149</v>
+        <v>975486</v>
       </c>
     </row>
     <row r="16">
